--- a/reports/pdf_rolling5_20261015.xlsx
+++ b/reports/pdf_rolling5_20261015.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-10-07 ~ 2026-10-15  (최근 5거래일)  ·  캡처 6/7  ·  대기: RISE</t>
+          <t>최근 5거래일 변화  ·  2026-10-07 ~ 2026-10-15  (최근 5거래일)  ·  캡처 5/7  ·  대기: RISE, TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,127억   ·   현금 176억(3.5%)      오늘 2026-10-15  vs  5일전 2026-10-07      매수 11종목  /  매도 24종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,947억   ·   현금 88억(1.8%)      오늘 2026-10-15  vs  5일전 2026-10-07      매수 11종목  /  매도 24종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>489</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>3329196138</v>
+        <v>3325834087</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-359</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-3685767956</v>
+        <v>-3682045815</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>176</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>2839493340</v>
+        <v>2836625825</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-99</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1757132722</v>
+        <v>-1755358249</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>69</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>5196805573</v>
+        <v>5191557483</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-88</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1447653238</v>
+        <v>-1446191299</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>57</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>2880837872</v>
+        <v>2877928605</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-81</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1286744520</v>
+        <v>-1285445077</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>46</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>2140263348</v>
+        <v>2138101963</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-80</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-2362544715</v>
+        <v>-2360158856</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>41</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>3258607186</v>
+        <v>3255316422</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-59</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-2151659851</v>
+        <v>-2149486958</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>38</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1463013743</v>
+        <v>1461536291</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-55</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-3112236442</v>
+        <v>-3109093493</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>32</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1523762061</v>
+        <v>1522223262</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>-39</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-1109226636</v>
+        <v>-1108106463</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>28</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>474490944</v>
+        <v>474011770</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>-31</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-2976865801</v>
+        <v>-2973859558</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>27</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>957900890</v>
+        <v>956933536</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>-23</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-1016568108</v>
+        <v>-1015541508</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>5</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1357670411</v>
+        <v>1356299342</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>-21</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-964590142</v>
+        <v>-963616033</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>-18</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-1496608653</v>
+        <v>-1495097275</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>-16</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-352003307</v>
+        <v>-351647830</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>-15</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-2095965634</v>
+        <v>-2093848985</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1236,23 +1236,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-786061438</v>
+        <v>-474011770</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.32%→0.12%</t>
+          <t>0.18%→0.10%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>21→9</t>
+          <t>24→12</t>
         </is>
       </c>
     </row>
@@ -1264,23 +1264,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>와이지엔터테인먼트</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-474490944</v>
+        <v>-403919804</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.18%→0.10%</t>
+          <t>0.58%→0.53%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>24→12</t>
+          <t>88→76</t>
         </is>
       </c>
     </row>
@@ -1292,23 +1292,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-404328122</v>
+        <v>-785267619</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.53%</t>
+          <t>0.32%→0.12%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>88→76</t>
+          <t>21→9</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
         <v>-11</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-575572974</v>
+        <v>-574991721</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>-8</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-1906684577</v>
+        <v>-1904759076</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>-7</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-450211436</v>
+        <v>-449756782</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>-6</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-135271541</v>
+        <v>-135134934</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>-4</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-690529009</v>
+        <v>-689831666</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>-3</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-946900787</v>
+        <v>-945944541</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>-3</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-438220333</v>
+        <v>-437777788</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,017억   ·   현금 51억(1.7%)      오늘 2026-10-15  vs  5일전 2026-10-07      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,990억   ·   현금 25억(0.8%)      오늘 2026-10-15  vs  5일전 2026-10-07      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -1535,7 +1535,7 @@
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,650억   ·   현금 82억(3.1%)      오늘 2026-10-15  vs  5일전 2026-10-07      매수 9종목  /  매도 14종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,556억   ·   현금 41억(1.6%)      오늘 2026-10-15  vs  5일전 2026-10-07      매수 9종목  /  매도 14종목</t>
         </is>
       </c>
       <c r="B34" s="4" t="n"/>
@@ -1631,7 +1631,7 @@
         <v>46</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>6345238462</v>
+        <v>6335628115</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>-195</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-1230371702</v>
+        <v>-1228508210</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1805759562</v>
+        <v>1803024602</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>-149</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-4385962937</v>
+        <v>-4379320062</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>31</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1168265717</v>
+        <v>1166496289</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>-96</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-1603007611</v>
+        <v>-1600579734</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>21</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>3333329192</v>
+        <v>3328280611</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>-80</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-1578719617</v>
+        <v>-1576328526</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>19</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>736097822</v>
+        <v>734982945</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>-66</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-1261061694</v>
+        <v>-1259151720</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>15</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>871199789</v>
+        <v>869880290</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>-53</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-1285514688</v>
+        <v>-1283567679</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>14</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>1166087717</v>
+        <v>1164321589</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>-50</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-988349760</v>
+        <v>-986852829</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>13</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>4019729026</v>
+        <v>4013640840</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>-39</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-2350061430</v>
+        <v>-2346502083</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>10</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>2102099490</v>
+        <v>2098915701</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>-33</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-1258883695</v>
+        <v>-1256977020</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>-30</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-1635479604</v>
+        <v>-1633002545</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>-30</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-1473119643</v>
+        <v>-1470888491</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>-26</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-1376231666</v>
+        <v>-1374147259</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>-18</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-2667059353</v>
+        <v>-2663019889</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>-6</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-1073159740</v>
+        <v>-1071534358</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
     <row r="52" ht="19" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,933억   ·   현금 27억(1.4%)      오늘 2026-10-15  vs  5일전 2026-10-07      매수 6종목  /  매도 7종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,913억   ·   현금 14억(0.7%)      오늘 2026-10-15  vs  5일전 2026-10-07      매수 6종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B52" s="4" t="n"/>
@@ -2256,7 +2256,7 @@
         <v>149</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>10260648743</v>
+        <v>10260645528</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>-356</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-4479032736</v>
+        <v>-4479031332</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>125</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>1833612883</v>
+        <v>1833612308</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>-113</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-1155549541</v>
+        <v>-1155549179</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>58</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>932988195</v>
+        <v>932987903</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>-102</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-3566726545</v>
+        <v>-3566725427</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>53</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>874887083</v>
+        <v>874886809</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>-63</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-1012211761</v>
+        <v>-1012211444</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
@@ -2425,23 +2425,23 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B59" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>1358118284</v>
+        <v>257950473</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>4.64%→5.72%</t>
+          <t>11.84%→12.36%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>21→24</t>
+          <t>270→273</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr">
@@ -2453,7 +2453,7 @@
         <v>-34</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-5267400100</v>
+        <v>-5267398450</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
@@ -2469,23 +2469,23 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="B60" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>257950554</v>
+        <v>1358117858</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>11.84%→12.36%</t>
+          <t>4.64%→5.72%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>270→273</t>
+          <t>21→24</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -2497,7 +2497,7 @@
         <v>-12</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-106397422</v>
+        <v>-106397389</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>-4</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-34010407</v>
+        <v>-34010396</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
     <row r="63" ht="19" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 306억   ·   현금 7억(2.3%)      오늘 2026-10-15  vs  5일전 2026-10-07      매수 4종목  /  매도 8종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 296억   ·   현금 3억(1.2%)      오늘 2026-10-15  vs  5일전 2026-10-07      매수 4종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B63" s="4" t="n"/>
@@ -2637,11 +2637,11 @@
         <v>89</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>92293000</v>
+        <v>97077640</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.30%</t>
+          <t>0.00%→0.33%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
@@ -2658,11 +2658,11 @@
         <v>-76</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-56331200</v>
+        <v>-60340200</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
-          <t>1.54%→1.37%</t>
+          <t>1.71%→1.52%</t>
         </is>
       </c>
       <c r="K66" s="13" t="inlineStr">
@@ -2681,11 +2681,11 @@
         <v>42</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>12880560</v>
+        <v>12536370</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>2.58%→2.64%</t>
+          <t>2.61%→2.66%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
@@ -2702,11 +2702,11 @@
         <v>-60</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-51204000</v>
+        <v>-64038600</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>0.62%→0.45%</t>
+          <t>0.80%→0.58%</t>
         </is>
       </c>
       <c r="K67" s="13" t="inlineStr">
@@ -2725,11 +2725,11 @@
         <v>5</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>50694000</v>
+        <v>46498000</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>2.86%→3.05%</t>
+          <t>2.72%→2.90%</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
@@ -2746,11 +2746,11 @@
         <v>-21</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-35985600</v>
+        <v>-37004100</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>2.82%→2.72%</t>
+          <t>3.00%→2.90%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
@@ -2769,11 +2769,11 @@
         <v>5</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>76330000</v>
+        <v>75207500</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>0.95%→1.21%</t>
+          <t>0.97%→1.24%</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
@@ -2790,11 +2790,11 @@
         <v>-17</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-28553200</v>
+        <v>-25570550</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>4.79%→4.72%</t>
+          <t>4.44%→4.38%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
@@ -2818,11 +2818,11 @@
         <v>-12</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-48388800</v>
+        <v>-44059200</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
-          <t>1.35%→1.20%</t>
+          <t>1.27%→1.13%</t>
         </is>
       </c>
       <c r="K70" s="13" t="inlineStr">
@@ -2846,11 +2846,11 @@
         <v>-10</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-53448000</v>
+        <v>-57620000</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>1.05%→0.88%</t>
+          <t>1.18%→0.99%</t>
         </is>
       </c>
       <c r="K71" s="13" t="inlineStr">
@@ -2874,11 +2874,11 @@
         <v>-5</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-45220000</v>
+        <v>-42277000</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>2.67%→2.54%</t>
+          <t>2.59%→2.46%</t>
         </is>
       </c>
       <c r="K72" s="13" t="inlineStr">
@@ -2902,11 +2902,11 @@
         <v>-5</v>
       </c>
       <c r="I73" s="15" t="n">
-        <v>-73440000</v>
+        <v>-70015000</v>
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>3.57%→3.35%</t>
+          <t>3.53%→3.31%</t>
         </is>
       </c>
       <c r="K73" s="13" t="inlineStr">
@@ -2933,49 +2933,41 @@
       <c r="K75" s="20" t="n"/>
     </row>
     <row r="77" ht="19" customHeight="1">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,051억      오늘 2026-10-15  vs  5일전 2026-10-07      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="n"/>
-      <c r="C77" s="4" t="n"/>
-      <c r="D77" s="4" t="n"/>
-      <c r="E77" s="4" t="n"/>
-      <c r="F77" s="4" t="n"/>
-      <c r="G77" s="4" t="n"/>
-      <c r="H77" s="4" t="n"/>
-      <c r="I77" s="4" t="n"/>
-      <c r="J77" s="4" t="n"/>
-      <c r="K77" s="4" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="18" t="inlineStr">
-        <is>
-          <t>변화 없음 (구성종목 동일)</t>
-        </is>
-      </c>
+      <c r="A77" s="19" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B77" s="20" t="n"/>
+      <c r="C77" s="20" t="n"/>
+      <c r="D77" s="20" t="n"/>
+      <c r="E77" s="20" t="n"/>
+      <c r="F77" s="20" t="n"/>
+      <c r="G77" s="20" t="n"/>
+      <c r="H77" s="20" t="n"/>
+      <c r="I77" s="20" t="n"/>
+      <c r="J77" s="20" t="n"/>
+      <c r="K77" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="18">
+    <mergeCell ref="G64:K64"/>
+    <mergeCell ref="A53:E53"/>
     <mergeCell ref="A34:K34"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="G35:K35"/>
+    <mergeCell ref="A3:K3"/>
     <mergeCell ref="A77:K77"/>
     <mergeCell ref="A64:E64"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A78:K78"/>
-    <mergeCell ref="G53:K53"/>
-    <mergeCell ref="A75:K75"/>
-    <mergeCell ref="A3:K3"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A32:K32"/>
-    <mergeCell ref="G4:K4"/>
-    <mergeCell ref="G64:K64"/>
-    <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="G35:K35"/>
     <mergeCell ref="A63:K63"/>
     <mergeCell ref="A52:K52"/>
+    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="G53:K53"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A75:K75"/>
+    <mergeCell ref="G4:K4"/>
     <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/pdf_rolling5_20261015.xlsx
+++ b/reports/pdf_rolling5_20261015.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-10-07 ~ 2026-10-15  (최근 5거래일)  ·  캡처 5/7  ·  대기: RISE, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-10-07 ~ 2026-10-15  (최근 5거래일)  ·  캡처 6/7  ·  대기: RISE</t>
         </is>
       </c>
     </row>
@@ -1460,23 +1460,23 @@
       <c r="E28" s="17" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-945944541</v>
+        <v>-437777788</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>2.71%→2.92%</t>
+          <t>5.81%→5.41%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>48→45</t>
+          <t>183→180</t>
         </is>
       </c>
     </row>
@@ -1488,23 +1488,23 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-437777788</v>
+        <v>-945944541</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>5.81%→5.41%</t>
+          <t>2.71%→2.92%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>183→180</t>
+          <t>48→45</t>
         </is>
       </c>
     </row>
@@ -2425,23 +2425,23 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="B59" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>257950473</v>
+        <v>1358117858</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>11.84%→12.36%</t>
+          <t>4.64%→5.72%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>270→273</t>
+          <t>21→24</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr">
@@ -2469,23 +2469,23 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B60" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>1358117858</v>
+        <v>257950473</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>4.64%→5.72%</t>
+          <t>11.84%→12.36%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>21→24</t>
+          <t>270→273</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -2718,23 +2718,23 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B68" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>46498000</v>
+        <v>75207500</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>2.72%→2.90%</t>
+          <t>0.97%→1.24%</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>86→91</t>
+          <t>19→24</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
@@ -2762,23 +2762,23 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B69" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>75207500</v>
+        <v>46498000</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>0.97%→1.24%</t>
+          <t>2.72%→2.90%</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
-          <t>19→24</t>
+          <t>86→91</t>
         </is>
       </c>
       <c r="G69" s="14" t="inlineStr">
@@ -2933,41 +2933,49 @@
       <c r="K75" s="20" t="n"/>
     </row>
     <row r="77" ht="19" customHeight="1">
-      <c r="A77" s="19" t="inlineStr">
-        <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B77" s="20" t="n"/>
-      <c r="C77" s="20" t="n"/>
-      <c r="D77" s="20" t="n"/>
-      <c r="E77" s="20" t="n"/>
-      <c r="F77" s="20" t="n"/>
-      <c r="G77" s="20" t="n"/>
-      <c r="H77" s="20" t="n"/>
-      <c r="I77" s="20" t="n"/>
-      <c r="J77" s="20" t="n"/>
-      <c r="K77" s="20" t="n"/>
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,035억      오늘 2026-10-15  vs  5일전 2026-10-07      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="n"/>
+      <c r="C77" s="4" t="n"/>
+      <c r="D77" s="4" t="n"/>
+      <c r="E77" s="4" t="n"/>
+      <c r="F77" s="4" t="n"/>
+      <c r="G77" s="4" t="n"/>
+      <c r="H77" s="4" t="n"/>
+      <c r="I77" s="4" t="n"/>
+      <c r="J77" s="4" t="n"/>
+      <c r="K77" s="4" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
+    <mergeCell ref="A34:K34"/>
+    <mergeCell ref="A77:K77"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A78:K78"/>
+    <mergeCell ref="G53:K53"/>
+    <mergeCell ref="A75:K75"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="G4:K4"/>
     <mergeCell ref="G64:K64"/>
     <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A34:K34"/>
+    <mergeCell ref="A35:E35"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A35:E35"/>
     <mergeCell ref="G35:K35"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A77:K77"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="A2:K2"/>
     <mergeCell ref="A63:K63"/>
     <mergeCell ref="A52:K52"/>
-    <mergeCell ref="A32:K32"/>
-    <mergeCell ref="G53:K53"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A75:K75"/>
-    <mergeCell ref="G4:K4"/>
     <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/pdf_rolling5_20261015.xlsx
+++ b/reports/pdf_rolling5_20261015.xlsx
@@ -1236,23 +1236,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>와이지엔터테인먼트</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-474011770</v>
+        <v>-403919804</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.18%→0.10%</t>
+          <t>0.58%→0.53%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>24→12</t>
+          <t>88→76</t>
         </is>
       </c>
     </row>
@@ -1264,23 +1264,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-403919804</v>
+        <v>-474011770</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.53%</t>
+          <t>0.18%→0.10%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>88→76</t>
+          <t>24→12</t>
         </is>
       </c>
     </row>
@@ -1460,23 +1460,23 @@
       <c r="E28" s="17" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-437777788</v>
+        <v>-945944541</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>5.81%→5.41%</t>
+          <t>2.71%→2.92%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>183→180</t>
+          <t>48→45</t>
         </is>
       </c>
     </row>
@@ -1488,23 +1488,23 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-945944541</v>
+        <v>-437777788</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>2.71%→2.92%</t>
+          <t>5.81%→5.41%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>48→45</t>
+          <t>183→180</t>
         </is>
       </c>
     </row>
@@ -2025,18 +2025,18 @@
       <c r="E46" s="17" t="n"/>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>쎄트렉아이  (편출)</t>
+          <t>인텔리안테크  (편출)</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
         <v>-30</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-1633002545</v>
+        <v>-1470888491</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>0.57%→0.00%</t>
+          <t>0.51%→0.00%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
@@ -2053,18 +2053,18 @@
       <c r="E47" s="17" t="n"/>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크  (편출)</t>
+          <t>쎄트렉아이  (편출)</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-30</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-1470888491</v>
+        <v>-1633002545</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>0.51%→0.00%</t>
+          <t>0.57%→0.00%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -2718,23 +2718,23 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B68" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>75207500</v>
+        <v>46498000</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>0.97%→1.24%</t>
+          <t>2.72%→2.90%</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>19→24</t>
+          <t>86→91</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
@@ -2762,23 +2762,23 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B69" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>46498000</v>
+        <v>75207500</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>2.72%→2.90%</t>
+          <t>0.97%→1.24%</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
-          <t>86→91</t>
+          <t>19→24</t>
         </is>
       </c>
       <c r="G69" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20261015.xlsx
+++ b/reports/pdf_rolling5_20261015.xlsx
@@ -1236,23 +1236,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-403919804</v>
+        <v>-785267619</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.53%</t>
+          <t>0.32%→0.12%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>88→76</t>
+          <t>21→9</t>
         </is>
       </c>
     </row>
@@ -1292,23 +1292,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-785267619</v>
+        <v>-403919804</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>0.32%→0.12%</t>
+          <t>0.58%→0.53%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>21→9</t>
+          <t>88→76</t>
         </is>
       </c>
     </row>
@@ -2425,23 +2425,23 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B59" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>1358117858</v>
+        <v>257950473</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>4.64%→5.72%</t>
+          <t>11.84%→12.36%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>21→24</t>
+          <t>270→273</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr">
@@ -2469,23 +2469,23 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="B60" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>257950473</v>
+        <v>1358117858</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>11.84%→12.36%</t>
+          <t>4.64%→5.72%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>270→273</t>
+          <t>21→24</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -2867,23 +2867,23 @@
       <c r="E72" s="17" t="n"/>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H72" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-42277000</v>
+        <v>-70015000</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>2.59%→2.46%</t>
+          <t>3.53%→3.31%</t>
         </is>
       </c>
       <c r="K72" s="13" t="inlineStr">
         <is>
-          <t>90→85</t>
+          <t>74→69</t>
         </is>
       </c>
     </row>
@@ -2895,23 +2895,23 @@
       <c r="E73" s="17" t="n"/>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H73" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I73" s="15" t="n">
-        <v>-70015000</v>
+        <v>-42277000</v>
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>3.53%→3.31%</t>
+          <t>2.59%→2.46%</t>
         </is>
       </c>
       <c r="K73" s="13" t="inlineStr">
         <is>
-          <t>74→69</t>
+          <t>90→85</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261015.xlsx
+++ b/reports/pdf_rolling5_20261015.xlsx
@@ -1264,23 +1264,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>와이지엔터테인먼트</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-474011770</v>
+        <v>-403919804</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.18%→0.10%</t>
+          <t>0.58%→0.53%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>24→12</t>
+          <t>88→76</t>
         </is>
       </c>
     </row>
@@ -1292,23 +1292,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-403919804</v>
+        <v>-474011770</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.53%</t>
+          <t>0.18%→0.10%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>88→76</t>
+          <t>24→12</t>
         </is>
       </c>
     </row>
@@ -1460,23 +1460,23 @@
       <c r="E28" s="17" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-945944541</v>
+        <v>-437777788</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>2.71%→2.92%</t>
+          <t>5.81%→5.41%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>48→45</t>
+          <t>183→180</t>
         </is>
       </c>
     </row>
@@ -1488,23 +1488,23 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-437777788</v>
+        <v>-945944541</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>5.81%→5.41%</t>
+          <t>2.71%→2.92%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>183→180</t>
+          <t>48→45</t>
         </is>
       </c>
     </row>
@@ -2425,23 +2425,23 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="B59" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>257950473</v>
+        <v>1358117858</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>11.84%→12.36%</t>
+          <t>4.64%→5.72%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>270→273</t>
+          <t>21→24</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr">
@@ -2469,23 +2469,23 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B60" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>1358117858</v>
+        <v>257950473</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>4.64%→5.72%</t>
+          <t>11.84%→12.36%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>21→24</t>
+          <t>270→273</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
